--- a/Output/journal_tracker.xlsx
+++ b/Output/journal_tracker.xlsx
@@ -446,7 +446,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N5"/>
+  <dimension ref="A1:N14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -633,7 +633,7 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
@@ -642,35 +642,31 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>Bear Call</t>
+          <t>Bull Put</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>CE</t>
+          <t>PE</t>
         </is>
       </c>
       <c r="E4" s="3" t="n">
-        <v>24950</v>
+        <v>23650</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>25250</v>
+        <v>23350</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>23.45</v>
+        <v>41.8</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>5.5</v>
+        <v>21.2</v>
       </c>
       <c r="I4" s="3" t="n">
-        <v>90</v>
-      </c>
-      <c r="J4" s="3" t="n">
-        <v>49743</v>
-      </c>
-      <c r="K4" s="3" t="n">
-        <v>48218</v>
-      </c>
+        <v>87</v>
+      </c>
+      <c r="J4" s="3" t="n"/>
+      <c r="K4" s="3" t="n"/>
       <c r="L4" s="3" t="n"/>
       <c r="M4" s="3" t="n"/>
       <c r="N4" s="3">
@@ -680,7 +676,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
@@ -689,35 +685,31 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>Bear Call</t>
+          <t>Bull Put</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>CE</t>
+          <t>PE</t>
         </is>
       </c>
       <c r="E5" s="3" t="n">
-        <v>24900</v>
+        <v>23700</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>25200</v>
+        <v>23400</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>30.35</v>
+        <v>47.5</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>7.4</v>
+        <v>23.55</v>
       </c>
       <c r="I5" s="3" t="n">
-        <v>87</v>
-      </c>
-      <c r="J5" s="3" t="n">
-        <v>49798</v>
-      </c>
-      <c r="K5" s="3" t="n">
-        <v>47826</v>
-      </c>
+        <v>85</v>
+      </c>
+      <c r="J5" s="3" t="n"/>
+      <c r="K5" s="3" t="n"/>
       <c r="L5" s="3" t="n"/>
       <c r="M5" s="3" t="n"/>
       <c r="N5" s="3">
@@ -725,6 +717,401 @@
         <v/>
       </c>
     </row>
+    <row r="6">
+      <c r="A6" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>Bull Put</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>PE</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="n">
+        <v>23800</v>
+      </c>
+      <c r="F6" s="3" t="n">
+        <v>23500</v>
+      </c>
+      <c r="G6" s="3" t="n">
+        <v>61.4</v>
+      </c>
+      <c r="H6" s="3" t="n">
+        <v>29.65</v>
+      </c>
+      <c r="I6" s="3" t="n">
+        <v>82</v>
+      </c>
+      <c r="J6" s="3" t="n"/>
+      <c r="K6" s="3" t="n"/>
+      <c r="L6" s="3" t="n"/>
+      <c r="M6" s="3" t="n"/>
+      <c r="N6" s="3">
+        <f>N5-J6</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>Bull Put</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>PE</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="n">
+        <v>23850</v>
+      </c>
+      <c r="F7" s="3" t="n">
+        <v>23550</v>
+      </c>
+      <c r="G7" s="3" t="n">
+        <v>69.55</v>
+      </c>
+      <c r="H7" s="3" t="n">
+        <v>33.55</v>
+      </c>
+      <c r="I7" s="3" t="n">
+        <v>80</v>
+      </c>
+      <c r="J7" s="3" t="n"/>
+      <c r="K7" s="3" t="n"/>
+      <c r="L7" s="3" t="n"/>
+      <c r="M7" s="3" t="n"/>
+      <c r="N7" s="3">
+        <f>N6-J7</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>Bull Put</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>PE</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="n">
+        <v>23900</v>
+      </c>
+      <c r="F8" s="3" t="n">
+        <v>23600</v>
+      </c>
+      <c r="G8" s="3" t="n">
+        <v>75.7</v>
+      </c>
+      <c r="H8" s="3" t="n">
+        <v>36.45</v>
+      </c>
+      <c r="I8" s="3" t="n">
+        <v>78</v>
+      </c>
+      <c r="J8" s="3" t="n"/>
+      <c r="K8" s="3" t="n"/>
+      <c r="L8" s="3" t="n"/>
+      <c r="M8" s="3" t="n"/>
+      <c r="N8" s="3">
+        <f>N7-J8</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>Bull Put</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>PE</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="n">
+        <v>24000</v>
+      </c>
+      <c r="F9" s="3" t="n">
+        <v>23700</v>
+      </c>
+      <c r="G9" s="3" t="n">
+        <v>99.15000000000001</v>
+      </c>
+      <c r="H9" s="3" t="n">
+        <v>47.5</v>
+      </c>
+      <c r="I9" s="3" t="n">
+        <v>73</v>
+      </c>
+      <c r="J9" s="3" t="n"/>
+      <c r="K9" s="3" t="n"/>
+      <c r="L9" s="3" t="n"/>
+      <c r="M9" s="3" t="n"/>
+      <c r="N9" s="3">
+        <f>N8-J9</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>Bear Call</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>CE</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="n">
+        <v>24950</v>
+      </c>
+      <c r="F10" s="3" t="n">
+        <v>25250</v>
+      </c>
+      <c r="G10" s="3" t="n">
+        <v>23.45</v>
+      </c>
+      <c r="H10" s="3" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="I10" s="3" t="n">
+        <v>90</v>
+      </c>
+      <c r="J10" s="3" t="n">
+        <v>49743</v>
+      </c>
+      <c r="K10" s="3" t="n">
+        <v>48218</v>
+      </c>
+      <c r="L10" s="3" t="n"/>
+      <c r="M10" s="3" t="n"/>
+      <c r="N10" s="3">
+        <f>N9-J10</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>Bear Call</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>CE</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="n">
+        <v>24900</v>
+      </c>
+      <c r="F11" s="3" t="n">
+        <v>25200</v>
+      </c>
+      <c r="G11" s="3" t="n">
+        <v>30.35</v>
+      </c>
+      <c r="H11" s="3" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="I11" s="3" t="n">
+        <v>87</v>
+      </c>
+      <c r="J11" s="3" t="n">
+        <v>49798</v>
+      </c>
+      <c r="K11" s="3" t="n">
+        <v>47826</v>
+      </c>
+      <c r="L11" s="3" t="n"/>
+      <c r="M11" s="3" t="n"/>
+      <c r="N11" s="3">
+        <f>N10-J11</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>Bear Call</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>CE</t>
+        </is>
+      </c>
+      <c r="E12" s="3" t="n">
+        <v>24850</v>
+      </c>
+      <c r="F12" s="3" t="n">
+        <v>25150</v>
+      </c>
+      <c r="G12" s="3" t="n">
+        <v>37.4</v>
+      </c>
+      <c r="H12" s="3" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="I12" s="3" t="n">
+        <v>85</v>
+      </c>
+      <c r="J12" s="3" t="n"/>
+      <c r="K12" s="3" t="n"/>
+      <c r="L12" s="3" t="n"/>
+      <c r="M12" s="3" t="n"/>
+      <c r="N12" s="3">
+        <f>N11-J12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>Bear Call</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>CE</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="n">
+        <v>24800</v>
+      </c>
+      <c r="F13" s="3" t="n">
+        <v>25100</v>
+      </c>
+      <c r="G13" s="3" t="n">
+        <v>46</v>
+      </c>
+      <c r="H13" s="3" t="n">
+        <v>11.65</v>
+      </c>
+      <c r="I13" s="3" t="n">
+        <v>82</v>
+      </c>
+      <c r="J13" s="3" t="n"/>
+      <c r="K13" s="3" t="n"/>
+      <c r="L13" s="3" t="n"/>
+      <c r="M13" s="3" t="n"/>
+      <c r="N13" s="3">
+        <f>N12-J13</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>Bear Call</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>CE</t>
+        </is>
+      </c>
+      <c r="E14" s="3" t="n">
+        <v>24650</v>
+      </c>
+      <c r="F14" s="3" t="n">
+        <v>24950</v>
+      </c>
+      <c r="G14" s="3" t="n">
+        <v>83</v>
+      </c>
+      <c r="H14" s="3" t="n">
+        <v>23.45</v>
+      </c>
+      <c r="I14" s="3" t="n">
+        <v>73</v>
+      </c>
+      <c r="J14" s="3" t="n"/>
+      <c r="K14" s="3" t="n"/>
+      <c r="L14" s="3" t="n"/>
+      <c r="M14" s="3" t="n"/>
+      <c r="N14" s="3">
+        <f>N13-J14</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
